--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-course-of-encounter.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-course-of-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T12:47:35+00:00</t>
+    <t>2026-05-07T13:30:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-course-of-encounter.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-course-of-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="137">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Modèle logique métier - FR LM Course of encounter</t>
+    <t>Logical model - FR LM Course of encounter</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T13:30:39+00:00</t>
+    <t>2026-05-12T13:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -375,7 +375,7 @@
     <t>fr-lm-section.entry</t>
   </si>
   <si>
-    <t>fr-lm-course-of-encounter.entry.observation</t>
+    <t>fr-lm-course-of-encounter.entry.testResults</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-observation
@@ -385,7 +385,7 @@
     <t>Entrée Simple observation</t>
   </si>
   <si>
-    <t>fr-lm-course-of-encounter.entry.transfertPatient</t>
+    <t>fr-lm-course-of-encounter.entry.patientTransfer</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-transfer
@@ -395,7 +395,7 @@
     <t>Entrée Transfert du patient</t>
   </si>
   <si>
-    <t>fr-lm-course-of-encounter.entry.probleme</t>
+    <t>fr-lm-course-of-encounter.entry.diagnosticSummary</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-condition
@@ -403,6 +403,42 @@
   </si>
   <si>
     <t>Entrée Problème</t>
+  </si>
+  <si>
+    <t>fr-lm-course-of-encounter.entry.procedures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-procedure
+</t>
+  </si>
+  <si>
+    <t>Entrée Acte</t>
+  </si>
+  <si>
+    <t>fr-lm-course-of-encounter.entry.medicalDevicesAndImplants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device-use
+</t>
+  </si>
+  <si>
+    <t>Entrée Dispositif médical et implant</t>
+  </si>
+  <si>
+    <t>fr-lm-course-of-encounter.entry.medications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication-administration
+</t>
+  </si>
+  <si>
+    <t>Entrée Traitement administré pendant le séjour</t>
+  </si>
+  <si>
+    <t>fr-lm-course-of-encounter.entry.notes</t>
+  </si>
+  <si>
+    <t>Entrée Note</t>
   </si>
 </sst>
 </file>
@@ -704,11 +740,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ15"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.6953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.6953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="48.55078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="48.55078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -717,7 +753,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.52734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -738,7 +774,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.6328125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="48.55078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -2254,6 +2290,406 @@
         <v>73</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
